--- a/data/outputSpecialityRpt/File1/RPT_RPT3913152273708ME_outputSpecialityRpt.xlsx
+++ b/data/outputSpecialityRpt/File1/RPT_RPT3913152273708ME_outputSpecialityRpt.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Output| Specialty RPT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Output| Specialty RPT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -853,17 +853,17 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>00006022761</t>
+          <t>55513071001</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>ISENTRESS</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -877,51 +877,51 @@
         </is>
       </c>
       <c r="I15" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>0.1283536039590935</v>
+        <v>1.087700694425811</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>0.0426064343739576</v>
+        <v>1.117323113146661</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>0.03873118322978829</v>
+        <v>1.153887565251537</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>0.03493480694215503</v>
+        <v>1.180116296489632</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>0.03148906283071318</v>
+        <v>1.206118356353854</v>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>$22498.5615234375</t>
+          <t>$2250.52001953125</t>
         </is>
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>$1027.681505404215</t>
+          <t>$2677.974108328542</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>$358.01288302023227</t>
+          <t>$2947.0306769691756</t>
         </is>
       </c>
       <c r="R15" s="14" t="inlineStr">
         <is>
-          <t>$340.832275821994</t>
+          <t>$3253.215066426898</t>
         </is>
       </c>
       <c r="S15" s="14" t="inlineStr">
         <is>
-          <t>$321.2259349879383</t>
+          <t>$3549.1646458802707</t>
         </is>
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>$302.50587929786747</t>
+          <t>$3868.9476104273854</t>
         </is>
       </c>
       <c r="U15" s="14" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>00069068803</t>
+          <t>50881001060</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1017,51 +1017,51 @@
         </is>
       </c>
       <c r="I16" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>3.344907874268229</v>
+        <v>1.14584340540162</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>2.163257967262835</v>
+        <v>1.211569850049194</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>2.155468717336428</v>
+        <v>0.8273356695636447</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>2.248444968712019</v>
+        <v>0.5974247552928696</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>2.372222129759891</v>
+        <v>0.5975211678081918</v>
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>$237052.796875</t>
+          <t>$21120.0</t>
         </is>
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
-          <t>$204733.6637780323</t>
+          <t>$24441.21423114749</t>
         </is>
       </c>
       <c r="Q16" s="14" t="inlineStr">
         <is>
-          <t>$135809.5199415331</t>
+          <t>$26044.64003709972</t>
         </is>
       </c>
       <c r="R16" s="14" t="inlineStr">
         <is>
-          <t>$138819.08260701413</t>
+          <t>$17926.387653893486</t>
         </is>
       </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
-          <t>$148557.27957691043</t>
+          <t>$13048.30405093489</t>
         </is>
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>$160775.83847382886</t>
+          <t>$13153.262670131497</t>
         </is>
       </c>
       <c r="U16" s="14" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>49702022813</t>
+          <t>55513071021</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>TIVICAY</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1157,51 +1157,51 @@
         </is>
       </c>
       <c r="I17" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>1.710518446737362</v>
+        <v>3.263102083277433</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>1.291710330178022</v>
+        <v>3.351969339439983</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>0.1750612854719327</v>
+        <v>3.46166269575461</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>0.05298309646330671</v>
+        <v>3.540348889468897</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>0.01733822787306657</v>
+        <v>3.618355069061561</v>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>$5580.3798828125</t>
+          <t>$6751.56005859375</t>
         </is>
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>$5172.984238930389</t>
+          <t>$8097.390974080081</t>
         </is>
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>$4140.218590494925</t>
+          <t>$8734.378171370377</t>
         </is>
       </c>
       <c r="R17" s="14" t="inlineStr">
         <is>
-          <t>$592.661967657635</t>
+          <t>$9473.33611390536</t>
         </is>
       </c>
       <c r="S17" s="14" t="inlineStr">
         <is>
-          <t>$188.65039190896815</t>
+          <t>$10175.81472467212</t>
         </is>
       </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>$64.91992927702988</t>
+          <t>$10921.662856388502</t>
         </is>
       </c>
       <c r="U17" s="14" t="inlineStr">
@@ -1273,17 +1273,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>50881000560</t>
+          <t>49702022813</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>TIVICAY</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1297,51 +1297,51 @@
         </is>
       </c>
       <c r="I18" s="14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>12.60427745941782</v>
+        <v>1.710518446737362</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>13.32726835054113</v>
+        <v>1.291710330178022</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>9.100692365200091</v>
+        <v>0.1750612854719327</v>
       </c>
       <c r="M18" s="14" t="n">
-        <v>6.571672308221566</v>
+        <v>0.05298309646330671</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>6.57273284589011</v>
+        <v>0.01733822787306657</v>
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>$253440.0</t>
+          <t>$5580.3798828125</t>
         </is>
       </c>
       <c r="P18" s="14" t="inlineStr">
         <is>
-          <t>$293294.57077376987</t>
+          <t>$5172.984238930389</t>
         </is>
       </c>
       <c r="Q18" s="14" t="inlineStr">
         <is>
-          <t>$312535.68044519663</t>
+          <t>$4140.218590494925</t>
         </is>
       </c>
       <c r="R18" s="14" t="inlineStr">
         <is>
-          <t>$215116.65184672183</t>
+          <t>$592.661967657635</t>
         </is>
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$156579.64861121867</t>
+          <t>$188.65039190896815</t>
         </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>$157839.152041578</t>
+          <t>$64.91992927702988</t>
         </is>
       </c>
       <c r="U18" s="14" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>50881001060</t>
+          <t>NEWGENERICS50881001060</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -1428,60 +1428,60 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I19" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="14" t="n">
-        <v>1.14584340540162</v>
+        <v>0</v>
       </c>
       <c r="K19" s="14" t="n">
-        <v>1.211569850049194</v>
+        <v>0</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>0.8273356695636447</v>
+        <v>0.4550994970956699</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>0.5974247552928696</v>
+        <v>0.7501972131735741</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>0.5975211678081918</v>
+        <v>0.8206709705551316</v>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>$21120.0</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>$24441.21423114749</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>$26044.64003709972</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R19" s="14" t="inlineStr">
         <is>
-          <t>$17926.387653893486</t>
+          <t>$8871.187829025292</t>
         </is>
       </c>
       <c r="S19" s="14" t="inlineStr">
         <is>
-          <t>$13048.30405093489</t>
+          <t>$14736.523913703204</t>
         </is>
       </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>$13153.262670131497</t>
+          <t>$16245.491894432682</t>
         </is>
       </c>
       <c r="U19" s="14" t="inlineStr">
@@ -1553,75 +1553,75 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>55513071001</t>
+          <t>NEWGENERICS59676056201</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>NEW GENERIC PREZISTA</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I20" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>1.087700694425811</v>
+        <v>1.757711967973708</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>1.117323113146661</v>
+        <v>1.748518629200126</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>1.153887565251537</v>
+        <v>1.747538729280607</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>1.180116296489632</v>
+        <v>1.733487252875713</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>1.206118356353854</v>
+        <v>1.716551696336842</v>
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>$2250.52001953125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P20" s="14" t="inlineStr">
         <is>
-          <t>$2677.974108328542</t>
+          <t>$13000.901002882863</t>
         </is>
       </c>
       <c r="Q20" s="14" t="inlineStr">
         <is>
-          <t>$2947.0306769691756</t>
+          <t>$13528.592045710888</t>
         </is>
       </c>
       <c r="R20" s="14" t="inlineStr">
         <is>
-          <t>$3253.215066426898</t>
+          <t>$14145.789238097454</t>
         </is>
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$3549.1646458802707</t>
+          <t>$14708.110870024144</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>$3868.9476104273854</t>
+          <t>$15266.131487089728</t>
         </is>
       </c>
       <c r="U20" s="14" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>55513071021</t>
+          <t>50881000560</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1717,51 +1717,51 @@
         </is>
       </c>
       <c r="I21" s="14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>3.263102083277433</v>
+        <v>12.60427745941782</v>
       </c>
       <c r="K21" s="14" t="n">
-        <v>3.351969339439983</v>
+        <v>13.32726835054113</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>3.46166269575461</v>
+        <v>9.100692365200091</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>3.540348889468897</v>
+        <v>6.571672308221566</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>3.618355069061561</v>
+        <v>6.57273284589011</v>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>$6751.56005859375</t>
+          <t>$253440.0</t>
         </is>
       </c>
       <c r="P21" s="14" t="inlineStr">
         <is>
-          <t>$8097.390974080081</t>
+          <t>$293294.57077376987</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>$8734.378171370377</t>
+          <t>$312535.68044519663</t>
         </is>
       </c>
       <c r="R21" s="14" t="inlineStr">
         <is>
-          <t>$9473.33611390536</t>
+          <t>$215116.65184672183</t>
         </is>
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$10175.81472467212</t>
+          <t>$156579.64861121867</t>
         </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>$10921.662856388502</t>
+          <t>$157839.152041578</t>
         </is>
       </c>
       <c r="U21" s="14" t="inlineStr">
@@ -1833,75 +1833,75 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>58406003204</t>
+          <t>NEWGENERICS00006022761</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>ENBREL SURECLICK</t>
+          <t>NEW GENERIC ISENTRESS</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I22" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>3.136500255765359</v>
+        <v>2.402670330840043</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>3.199183623829533</v>
+        <v>2.26227875244484</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>3.291564355509998</v>
+        <v>2.06062591633851</v>
       </c>
       <c r="M22" s="14" t="n">
-        <v>3.36516328195827</v>
+        <v>1.853817290376724</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>3.438062264015966</v>
+        <v>1.664857593211588</v>
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>$88102.078125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P22" s="14" t="inlineStr">
         <is>
-          <t>$95132.79043600707</t>
+          <t>$17311.479851602824</t>
         </is>
       </c>
       <c r="Q22" s="14" t="inlineStr">
         <is>
-          <t>$99526.99258182291</t>
+          <t>$17105.308456563875</t>
         </is>
       </c>
       <c r="R22" s="14" t="inlineStr">
         <is>
-          <t>$105048.43999602292</t>
+          <t>$16313.362674456386</t>
         </is>
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$110178.69594225998</t>
+          <t>$15330.91005725401</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>$115467.29148507121</t>
+          <t>$14382.512891998267</t>
         </is>
       </c>
       <c r="U22" s="14" t="inlineStr">
@@ -1973,75 +1973,75 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>59676056201</t>
+          <t>NEWGENERICS50881000560</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I23" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" s="14" t="n">
-        <v>1.217619846562761</v>
+        <v>0</v>
       </c>
       <c r="K23" s="14" t="n">
-        <v>1.215657977821603</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>1.212552309830595</v>
+        <v>5.00609446805237</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>1.205935661615686</v>
+        <v>8.252169344909316</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>1.198537421014869</v>
+        <v>9.027380676106448</v>
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>$23308.01953125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>$10008.01445901425</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q23" s="14" t="inlineStr">
         <is>
-          <t>$10452.794498342253</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R23" s="14" t="inlineStr">
         <is>
-          <t>$10910.29448017336</t>
+          <t>$106454.25394830349</t>
         </is>
       </c>
       <c r="S23" s="14" t="inlineStr">
         <is>
-          <t>$11376.577448020069</t>
+          <t>$176838.28696443842</t>
         </is>
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>$11853.322837166606</t>
+          <t>$194945.90273319217</t>
         </is>
       </c>
       <c r="U23" s="14" t="inlineStr">
@@ -2113,17 +2113,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>61958190101</t>
+          <t>00006022761</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>ISENTRESS</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -2140,48 +2140,48 @@
         <v>3</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>3.270672006301701</v>
+        <v>0.1283536039590935</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>3.414596135850205</v>
+        <v>0.0426064343739576</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>3.564361090246219</v>
+        <v>0.03873118322978829</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>3.712802749250202</v>
+        <v>0.03493480694215503</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>3.864789681528603</v>
+        <v>0.03148906283071318</v>
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>$45533.8798828125</t>
+          <t>$22498.5615234375</t>
         </is>
       </c>
       <c r="P24" s="14" t="inlineStr">
         <is>
-          <t>$53241.713277062925</t>
+          <t>$1027.681505404215</t>
         </is>
       </c>
       <c r="Q24" s="14" t="inlineStr">
         <is>
-          <t>$58710.08456267025</t>
+          <t>$358.01288302023227</t>
         </is>
       </c>
       <c r="R24" s="14" t="inlineStr">
         <is>
-          <t>$64741.406073179955</t>
+          <t>$340.832275821994</t>
         </is>
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>$71243.96275733654</t>
+          <t>$321.2259349879383</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
-          <t>$78337.07273684425</t>
+          <t>$302.50587929786747</t>
         </is>
       </c>
       <c r="U24" s="14" t="inlineStr">
@@ -2253,75 +2253,75 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00006022761</t>
+          <t>58406003204</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC ISENTRESS</t>
+          <t>ENBREL SURECLICK</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>2.402670330840043</v>
+        <v>3.136500255765359</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>2.26227875244484</v>
+        <v>3.199183623829533</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>2.060625916338511</v>
+        <v>3.291564355509998</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>1.853817290376724</v>
+        <v>3.36516328195827</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>1.664857593211587</v>
+        <v>3.438062264015966</v>
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$88102.078125</t>
         </is>
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>$17311.479851602824</t>
+          <t>$95132.79043600707</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>$17105.308456563875</t>
+          <t>$99526.99258182291</t>
         </is>
       </c>
       <c r="R25" s="14" t="inlineStr">
         <is>
-          <t>$16313.362674456386</t>
+          <t>$105048.43999602292</t>
         </is>
       </c>
       <c r="S25" s="14" t="inlineStr">
         <is>
-          <t>$15330.91005725401</t>
+          <t>$110178.69594225998</t>
         </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>$14382.512891998267</t>
+          <t>$115467.29148507121</t>
         </is>
       </c>
       <c r="U25" s="14" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00069068803</t>
+          <t>00069068803</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC IBRANCE</t>
+          <t>IBRANCE</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2408,60 +2408,60 @@
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I26" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>1.220807223584646</v>
+        <v>3.344907874268229</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>2.635178875703777</v>
+        <v>2.163257967262835</v>
       </c>
       <c r="L26" s="14" t="n">
-        <v>2.955962465086986</v>
+        <v>2.155468717336428</v>
       </c>
       <c r="M26" s="14" t="n">
-        <v>3.139440339058244</v>
+        <v>2.248444968712019</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>3.300153187667277</v>
+        <v>2.372222129759891</v>
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$237052.796875</t>
         </is>
       </c>
       <c r="P26" s="14" t="inlineStr">
         <is>
-          <t>$67242.17049296676</t>
+          <t>$204733.6637780323</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr">
         <is>
-          <t>$148865.2502840881</t>
+          <t>$135809.5199415331</t>
         </is>
       </c>
       <c r="R26" s="14" t="inlineStr">
         <is>
-          <t>$171265.8384290979</t>
+          <t>$138819.08260701413</t>
         </is>
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>$186557.4782251351</t>
+          <t>$148557.27957691043</t>
         </is>
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>$201132.90501603944</t>
+          <t>$160775.83847382886</t>
         </is>
       </c>
       <c r="U26" s="14" t="inlineStr">
@@ -2533,17 +2533,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS49702022813</t>
+          <t>NEWGENERICS00069068803</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC TIVICAY</t>
+          <t>NEW GENERIC IBRANCE</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -2560,19 +2560,19 @@
         <v>0</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>0</v>
+        <v>1.220807223584646</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>0.2674065587106465</v>
+        <v>2.635178875703777</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>1.226878238151602</v>
+        <v>2.955962465086985</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>1.206732057718833</v>
+        <v>3.139440339058244</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>1.1134790910304</v>
+        <v>3.300153187667278</v>
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
@@ -2581,27 +2581,27 @@
       </c>
       <c r="P27" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$67242.17049296676</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>$771.2435104128266</t>
+          <t>$148865.2502840881</t>
         </is>
       </c>
       <c r="R27" s="14" t="inlineStr">
         <is>
-          <t>$3736.653200232335</t>
+          <t>$171265.8384290979</t>
         </is>
       </c>
       <c r="S27" s="14" t="inlineStr">
         <is>
-          <t>$3864.381363773408</t>
+          <t>$186557.4782251351</t>
         </is>
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>$3749.203331734332</t>
+          <t>$201132.90501603944</t>
         </is>
       </c>
       <c r="U27" s="14" t="inlineStr">
@@ -2673,75 +2673,75 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881000560</t>
+          <t>59676056201</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>0</v>
+        <v>1.217619846562761</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0</v>
+        <v>1.215657977821603</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>5.00609446805237</v>
+        <v>1.212552309830595</v>
       </c>
       <c r="M28" s="14" t="n">
-        <v>8.252169344909316</v>
+        <v>1.205935661615686</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>9.027380676106446</v>
+        <v>1.198537421014869</v>
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23308.01953125</t>
         </is>
       </c>
       <c r="P28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$10008.01445901425</t>
         </is>
       </c>
       <c r="Q28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$10452.794498342253</t>
         </is>
       </c>
       <c r="R28" s="14" t="inlineStr">
         <is>
-          <t>$106454.25394830349</t>
+          <t>$10910.29448017336</t>
         </is>
       </c>
       <c r="S28" s="14" t="inlineStr">
         <is>
-          <t>$176838.28696443842</t>
+          <t>$11376.577448020069</t>
         </is>
       </c>
       <c r="T28" s="14" t="inlineStr">
         <is>
-          <t>$194945.90273319217</t>
+          <t>$11853.322837166606</t>
         </is>
       </c>
       <c r="U28" s="14" t="inlineStr">
@@ -2813,75 +2813,75 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881001060</t>
+          <t>61958190101</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>0</v>
+        <v>3.270672006301701</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>0</v>
+        <v>3.414596135850205</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>0.45509949709567</v>
+        <v>3.564361090246219</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>0.7501972131735741</v>
+        <v>3.712802749250202</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>0.8206709705551314</v>
+        <v>3.864789681528603</v>
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$45533.8798828125</t>
         </is>
       </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$53241.713277062925</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$58710.08456267025</t>
         </is>
       </c>
       <c r="R29" s="14" t="inlineStr">
         <is>
-          <t>$8871.187829025292</t>
+          <t>$64741.406073179955</t>
         </is>
       </c>
       <c r="S29" s="14" t="inlineStr">
         <is>
-          <t>$14736.523913703204</t>
+          <t>$71243.96275733654</t>
         </is>
       </c>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>$16245.491894432682</t>
+          <t>$78337.07273684425</t>
         </is>
       </c>
       <c r="U29" s="14" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS59676056201</t>
+          <t>NEWGENERICS49702022813</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC PREZISTA</t>
+          <t>NEW GENERIC TIVICAY</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2980,19 +2980,19 @@
         <v>0</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>1.757711967973708</v>
+        <v>0</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>1.748518629200126</v>
+        <v>0.2674065587106465</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>1.747538729280608</v>
+        <v>1.226878238151602</v>
       </c>
       <c r="M30" s="14" t="n">
-        <v>1.733487252875713</v>
+        <v>1.206732057718833</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>1.716551696336842</v>
+        <v>1.113479091030401</v>
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
@@ -3001,27 +3001,27 @@
       </c>
       <c r="P30" s="14" t="inlineStr">
         <is>
-          <t>$13000.901002882862</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q30" s="14" t="inlineStr">
         <is>
-          <t>$13528.592045710888</t>
+          <t>$771.2435104128266</t>
         </is>
       </c>
       <c r="R30" s="14" t="inlineStr">
         <is>
-          <t>$14145.789238097454</t>
+          <t>$3736.653200232335</t>
         </is>
       </c>
       <c r="S30" s="14" t="inlineStr">
         <is>
-          <t>$14708.110870024144</t>
+          <t>$3864.381363773408</t>
         </is>
       </c>
       <c r="T30" s="14" t="inlineStr">
         <is>
-          <t>$15266.131487089728</t>
+          <t>$3749.203331734332</t>
         </is>
       </c>
       <c r="U30" s="14" t="inlineStr">
